--- a/Result/profitability/1526.xlsx
+++ b/Result/profitability/1526.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.02</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.18375</v>
+        <v>-0.16625</v>
       </c>
       <c r="N2" t="n">
-        <v>17.965</v>
+        <v>19.61375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.11</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.10625</v>
+        <v>-0.09874999999999998</v>
       </c>
       <c r="N3" t="n">
-        <v>19.01</v>
+        <v>19.35875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.04374999999999999</v>
+        <v>-0.14</v>
       </c>
       <c r="N4" t="n">
-        <v>19.03625</v>
+        <v>17.725</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09375</v>
+        <v>-0.075</v>
       </c>
       <c r="N5" t="n">
-        <v>16.81625</v>
+        <v>17.0475</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.04625</v>
+        <v>-0.1025</v>
       </c>
       <c r="N6" t="n">
-        <v>15.79375</v>
+        <v>17.47625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1266,16 +1266,16 @@
         <v>-0.19</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.08</v>
+        <v>-0.1175</v>
       </c>
       <c r="N7" t="n">
-        <v>16.57125</v>
+        <v>15.50625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1393,10 +1393,10 @@
         <v>-0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.08124999999999999</v>
+        <v>-0.0725</v>
       </c>
       <c r="N8" t="n">
-        <v>14.91125</v>
+        <v>16.00375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1526</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>168</v>
+      </c>
+      <c r="D75" t="n">
+        <v>132</v>
+      </c>
+      <c r="E75" t="n">
+        <v>36</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-23</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-13.96%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-27</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-22</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.2325</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.6925</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1590909090909091</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.6947535771065183</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.2884615384615385</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.850000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.09501797637390874</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
